--- a/data/trans_orig/Q46-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su peso</t>
+          <t>Población según su peso (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,24; 74,02</t>
+          <t>72,33; 74,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,52; 74,75</t>
+          <t>72,51; 74,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,44; 73,97</t>
+          <t>71,44; 74,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,23; 76,51</t>
+          <t>71,99; 76,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,28; 60,08</t>
+          <t>58,22; 60,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,46; 61,56</t>
+          <t>59,45; 61,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,39; 61,51</t>
+          <t>59,4; 61,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,21; 63,77</t>
+          <t>59,98; 63,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,52; 67,05</t>
+          <t>65,56; 67,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,28; 68,05</t>
+          <t>66,33; 68,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,82; 67,75</t>
+          <t>65,76; 67,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,33; 70,7</t>
+          <t>67,26; 70,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,79; 78,54</t>
+          <t>76,73; 78,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,8; 80,78</t>
+          <t>78,69; 80,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,24; 79,51</t>
+          <t>77,29; 79,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,92; 81,12</t>
+          <t>77,89; 81,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,24; 64,13</t>
+          <t>62,16; 63,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,75; 66,96</t>
+          <t>64,74; 66,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,86; 66,85</t>
+          <t>64,74; 66,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,22; 70,34</t>
+          <t>64,28; 69,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,18; 71,67</t>
+          <t>70,19; 71,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72,43; 74,13</t>
+          <t>72,44; 74,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,36; 73,16</t>
+          <t>71,36; 73,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,58; 74,33</t>
+          <t>69,35; 74,28</t>
         </is>
       </c>
     </row>
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,41; 81,25</t>
+          <t>79,43; 81,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,9; 83,87</t>
+          <t>81,98; 84,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,33; 82,57</t>
+          <t>80,47; 82,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,79; 83,31</t>
+          <t>80,84; 83,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,1; 66,04</t>
+          <t>64,09; 65,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,43; 68,24</t>
+          <t>66,32; 68,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,1; 68,08</t>
+          <t>66,03; 68,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,51; 396,7</t>
+          <t>67,6; 360,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,11; 75,78</t>
+          <t>74,12; 75,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,54; 75,29</t>
+          <t>73,54; 75,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,65; 219,98</t>
+          <t>74,69; 258,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,42; 81,6</t>
+          <t>79,45; 81,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,05; 83,3</t>
+          <t>81,1; 83,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,04; 84,48</t>
+          <t>82,05; 84,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,13; 95,18</t>
+          <t>83,08; 94,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,75; 67,92</t>
+          <t>65,83; 67,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 69,81</t>
+          <t>67,82; 69,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,92; 70,39</t>
+          <t>67,81; 70,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,4; 71,25</t>
+          <t>68,45; 71,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,84; 74,56</t>
+          <t>72,84; 74,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,62; 76,4</t>
+          <t>74,54; 76,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75,26; 77,05</t>
+          <t>75,28; 77,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,96; 88,81</t>
+          <t>75,95; 87,74</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,13; 80,46</t>
+          <t>78,16; 80,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,6; 81,14</t>
+          <t>78,8; 81,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,02; 83,62</t>
+          <t>81,05; 83,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,02; 84,42</t>
+          <t>81,94; 84,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,71; 69,7</t>
+          <t>67,71; 69,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,31; 72,94</t>
+          <t>70,43; 73,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,87; 71,38</t>
+          <t>68,84; 71,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,83; 70,46</t>
+          <t>68,95; 70,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,1; 74,87</t>
+          <t>73,04; 74,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74,75; 76,72</t>
+          <t>74,7; 76,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75,12; 77,07</t>
+          <t>75,14; 77,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,73; 77,32</t>
+          <t>75,58; 77,26</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,79; 78,22</t>
+          <t>75,95; 78,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,46; 81,22</t>
+          <t>78,39; 81,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,42; 82,18</t>
+          <t>79,48; 82,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79,22; 81,46</t>
+          <t>79,27; 81,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69,49; 71,79</t>
+          <t>69,5; 71,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,07; 74,94</t>
+          <t>72,06; 74,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,14; 71,75</t>
+          <t>69,27; 71,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70,17; 79,46</t>
+          <t>70,19; 79,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72,71; 74,38</t>
+          <t>72,7; 74,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75,45; 77,44</t>
+          <t>75,5; 77,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74,35; 76,42</t>
+          <t>74,32; 76,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>74,87; 79,24</t>
+          <t>74,98; 79,27</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,06; 77,96</t>
+          <t>75,0; 77,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,67; 79,43</t>
+          <t>76,52; 79,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76,49; 79,26</t>
+          <t>76,68; 79,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75,31; 77,24</t>
+          <t>75,23; 77,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,15; 70,99</t>
+          <t>68,08; 70,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,59; 72,09</t>
+          <t>69,78; 72,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,39; 72,23</t>
+          <t>69,34; 72,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,14; 69,6</t>
+          <t>68,09; 69,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,13; 73,3</t>
+          <t>71,28; 73,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,76; 74,8</t>
+          <t>72,76; 74,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,52; 74,59</t>
+          <t>72,41; 74,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,29; 72,53</t>
+          <t>71,25; 72,5</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,56; 78,36</t>
+          <t>77,57; 78,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,45; 80,33</t>
+          <t>79,4; 80,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,51; 80,47</t>
+          <t>79,48; 80,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,32; 86,05</t>
+          <t>80,3; 86,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,1; 65,97</t>
+          <t>65,11; 65,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,55; 68,43</t>
+          <t>67,54; 68,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,23; 68,13</t>
+          <t>67,22; 68,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,34; 129,69</t>
+          <t>68,42; 149,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,33; 71,99</t>
+          <t>71,35; 71,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73,52; 74,22</t>
+          <t>73,49; 74,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,33; 74,1</t>
+          <t>73,32; 74,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,57; 105,93</t>
+          <t>74,75; 107,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q46-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74,19</t>
+          <t>74,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,88</t>
+          <t>61,78</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,84</t>
+          <t>68,31</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 74,18</t>
+          <t>72,34; 74,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,51; 74,8</t>
+          <t>72,51; 74,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,44; 74,06</t>
+          <t>71,53; 74,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71,99; 76,36</t>
+          <t>72,19; 76,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,22; 60,11</t>
+          <t>58,23; 60,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,45; 61,6</t>
+          <t>59,52; 61,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,4; 61,55</t>
+          <t>59,47; 61,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,98; 63,99</t>
+          <t>60,18; 63,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,56; 67,1</t>
+          <t>65,44; 67,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,33; 68,06</t>
+          <t>66,35; 68,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,76; 67,71</t>
+          <t>65,8; 67,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,26; 70,56</t>
+          <t>66,83; 69,9</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79,47</t>
+          <t>78,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,53</t>
+          <t>67,6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,4</t>
+          <t>73,12</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,73; 78,51</t>
+          <t>76,8; 78,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,69; 80,69</t>
+          <t>78,77; 80,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,29; 79,42</t>
+          <t>77,26; 79,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,89; 81,26</t>
+          <t>77,47; 80,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,16; 63,99</t>
+          <t>62,19; 64,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,74; 66,93</t>
+          <t>64,77; 66,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,74; 66,77</t>
+          <t>64,74; 66,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,28; 69,96</t>
+          <t>65,79; 73,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,19; 71,64</t>
+          <t>70,2; 71,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72,44; 74,06</t>
+          <t>72,38; 74,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,36; 73,06</t>
+          <t>71,41; 73,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,35; 74,28</t>
+          <t>71,93; 75,37</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82,0</t>
+          <t>81,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>145,59</t>
+          <t>69,27</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>115,33</t>
+          <t>75,47</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,43; 81,28</t>
+          <t>79,26; 81,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,98; 84,03</t>
+          <t>81,92; 83,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,47; 82,64</t>
+          <t>80,4; 82,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,84; 83,37</t>
+          <t>80,58; 83,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,09; 65,96</t>
+          <t>64,05; 65,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,32; 68,21</t>
+          <t>66,43; 68,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,03; 68,06</t>
+          <t>66,01; 68,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,6; 360,85</t>
+          <t>67,59; 72,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,6; 73,14</t>
+          <t>71,56; 73,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,12; 75,81</t>
+          <t>74,12; 75,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,54; 75,19</t>
+          <t>73,57; 75,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,69; 258,17</t>
+          <t>74,38; 77,18</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88,07</t>
+          <t>83,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,41</t>
+          <t>69,54</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,02</t>
+          <t>76,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,45; 81,56</t>
+          <t>79,43; 81,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,1; 83,39</t>
+          <t>81,09; 83,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,05; 84,44</t>
+          <t>82,05; 84,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,08; 94,47</t>
+          <t>82,38; 84,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,83; 67,85</t>
+          <t>65,74; 67,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,82; 69,84</t>
+          <t>67,85; 69,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,81; 70,15</t>
+          <t>67,9; 70,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,45; 71,29</t>
+          <t>68,63; 71,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,84; 74,59</t>
+          <t>72,76; 74,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,54; 76,37</t>
+          <t>74,6; 76,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75,28; 77,07</t>
+          <t>75,17; 76,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,95; 87,74</t>
+          <t>75,51; 77,35</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83,11</t>
+          <t>83,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,64</t>
+          <t>69,88</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,45</t>
+          <t>76,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,16; 80,35</t>
+          <t>78,17; 80,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 81,34</t>
+          <t>78,68; 81,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,05; 83,62</t>
+          <t>81,1; 83,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,94; 84,18</t>
+          <t>81,98; 84,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,71; 69,68</t>
+          <t>67,66; 69,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,43; 73,01</t>
+          <t>70,3; 73,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,84; 71,24</t>
+          <t>68,98; 71,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,95; 70,48</t>
+          <t>69,15; 70,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,04; 74,81</t>
+          <t>73,04; 74,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74,7; 76,63</t>
+          <t>74,77; 76,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75,14; 77,21</t>
+          <t>75,13; 76,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,58; 77,26</t>
+          <t>75,66; 77,27</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80,27</t>
+          <t>80,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,54</t>
+          <t>70,54</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,7</t>
+          <t>75,21</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,95; 78,14</t>
+          <t>75,8; 78,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,39; 81,19</t>
+          <t>78,47; 81,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,48; 82,42</t>
+          <t>79,54; 82,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79,27; 81,44</t>
+          <t>79,25; 81,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69,5; 71,83</t>
+          <t>69,52; 71,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,06; 74,86</t>
+          <t>72,15; 74,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,27; 71,76</t>
+          <t>69,3; 71,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70,19; 79,19</t>
+          <t>69,74; 71,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72,7; 74,34</t>
+          <t>72,72; 74,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75,5; 77,61</t>
+          <t>75,47; 77,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74,32; 76,45</t>
+          <t>74,35; 76,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>74,98; 79,27</t>
+          <t>74,5; 76,03</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76,21</t>
+          <t>76,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>68,85</t>
+          <t>68,89</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,87</t>
+          <t>71,91</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,0; 77,87</t>
+          <t>75,04; 77,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,52; 79,57</t>
+          <t>76,54; 79,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76,68; 79,26</t>
+          <t>76,54; 79,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75,23; 77,28</t>
+          <t>75,28; 77,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,08; 70,87</t>
+          <t>68,17; 71,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,78; 72,16</t>
+          <t>69,72; 72,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,34; 72,27</t>
+          <t>69,29; 72,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,09; 69,61</t>
+          <t>68,17; 69,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,28; 73,47</t>
+          <t>71,21; 73,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,76; 74,84</t>
+          <t>72,76; 74,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,41; 74,66</t>
+          <t>72,45; 74,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,25; 72,5</t>
+          <t>71,32; 72,65</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81,88</t>
+          <t>80,37</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,67</t>
+          <t>68,57</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>81,77</t>
+          <t>74,33</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,57; 78,36</t>
+          <t>77,55; 78,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,4; 80,34</t>
+          <t>79,43; 80,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,48; 80,41</t>
+          <t>79,44; 80,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,3; 86,48</t>
+          <t>79,88; 80,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,11; 65,94</t>
+          <t>65,13; 65,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,54; 68,46</t>
+          <t>67,59; 68,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,22; 68,11</t>
+          <t>67,21; 68,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,42; 149,16</t>
+          <t>68,03; 69,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,35; 71,98</t>
+          <t>71,35; 72,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73,49; 74,21</t>
+          <t>73,5; 74,19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,32; 74,07</t>
+          <t>73,31; 74,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,75; 107,21</t>
+          <t>73,95; 74,9</t>
         </is>
       </c>
     </row>
